--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-pr-biobank-zellinie-organoid.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-pr-biobank-zellinie-organoid.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-02</t>
+    <t>2026-09-10</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -636,7 +636,7 @@
 </t>
   </si>
   <si>
-    <t>Infektiositätsstatus</t>
+    <t>MII EX Biobank Infektiositätsstatus</t>
   </si>
   <si>
     <t>Extension zur Angabe des Infektiositätsstatus einer Probe anhand der Biosafety-Level-Einstufung (BSL-1 bis BSL-4, SNOMED CT) bzw. der Angabe, dass keine Infektionsgefahr bekannt ist.</t>
@@ -1017,7 +1017,7 @@
     <t>miabis-type</t>
   </si>
   <si>
-    <t>https://fhir.bbmri-eric.eu/fhir/ValueSet/miabis-detailed-sample-type-vs</t>
+    <t>https://fhir.bbmri-eric.eu/ValueSet/miabis-detailed-sample-type-vs</t>
   </si>
   <si>
     <t>Specimen.type.coding:miabis-type.id</t>
@@ -1029,7 +1029,7 @@
     <t>Specimen.type.coding:miabis-type.system</t>
   </si>
   <si>
-    <t>https://fhir.bbmri-eric.eu/fhir/CodeSystem/miabis-detailed-samply-type-cs</t>
+    <t>https://fhir.bbmri-eric.eu/CodeSystem/miabis-detailed-samply-type-cs</t>
   </si>
   <si>
     <t>Specimen.type.coding:miabis-type.version</t>
@@ -1711,7 +1711,7 @@
     <t>temperature-miabis</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/fhir/StructureDefinition/miabis-sample-storage-temperature-extension}
+    <t xml:space="preserve">Extension {https://fhir.bbmri-eric.eu/StructureDefinition/miabis-sample-storage-temperature-extension}
 </t>
   </si>
   <si>
